--- a/assets/Model_Details.xlsx
+++ b/assets/Model_Details.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="40">
   <si>
     <t>Synthesizer</t>
   </si>
@@ -31,13 +31,13 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Number of dataset - Wins</t>
-  </si>
-  <si>
-    <t>Number of dataset - Timeout</t>
-  </si>
-  <si>
-    <t>Number of dataset - Errors</t>
+    <t>Number of datasets - Wins</t>
+  </si>
+  <si>
+    <t>Number of datasets - Timeout</t>
+  </si>
+  <si>
+    <t>Number of datasets - Errors</t>
   </si>
   <si>
     <t>On the Pareto Curve</t>
@@ -85,6 +85,9 @@
     <t>sdv</t>
   </si>
   <si>
+    <t>sdgym</t>
+  </si>
+  <si>
     <t>realtabformer</t>
   </si>
   <si>
@@ -100,37 +103,48 @@
     <t>Deep Learning</t>
   </si>
   <si>
-    <t>Hierarchical Modeling Algorithm synthesizer for multi-table data that learns table-level relationships and generates data while preserving them.</t>
-  </si>
-  <si>
-    <t>Hierarchical Sampling Algorithm synthesizer that generates multi-table data by sequentially sampling tables while maintaining relational consistency.</t>
-  </si>
-  <si>
-    <t>Statistical baseline synthesizer that models and samples each column independently, without learning relationships between columns and tables.</t>
-  </si>
-  <si>
-    <t>Multi-table baseline synthesizer that generates data uniformly at random for each table while preserving table schemas.</t>
-  </si>
-  <si>
-    <t>Deep learning synthesizer based on Conditional GANs (CTGAN), designed to handle imbalanced categorical distributions in tabular data.</t>
-  </si>
-  <si>
-    <t>Lightweight statistical synthesizer that applies simple, column-wise models without learning inter-column dependencies.</t>
-  </si>
-  <si>
-    <t>GAN-based synthesizer that combines copula modeling with deep learning to better capture dependencies between tabular columns.</t>
-  </si>
-  <si>
-    <t>Statistical synthesizer that models each column's marginal distribution and captures inter-column dependencies using a Gaussian copula.</t>
-  </si>
-  <si>
-    <t>Transformer-based deep learning synthesizer that treats tabular data as a sequence modeling problem, inspired by large language models.</t>
-  </si>
-  <si>
-    <t>Deep learning synthesizer based on a Variational Autoencoder (TVAE), capable of modeling complex continuous and mixed-type tabular data.</t>
-  </si>
-  <si>
-    <t>Statistical baseline synthesizer that generates values uniformly at random within the observed bounds of each column.</t>
+    <t xml:space="preserve">The HMA Synthesizer uses hierarchical ML algorithm to learn from real data and generate synthetic data.  The algorithm uses classical statistics.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The HSA Synthesizer uses a segment-based algorithm to learn from your real data and generate synthetic data. This synthesizer offers fast performance for unlimited tables.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Independent Synthesizer learns each table's patterns independently. This synthesizer offers fast performance for unlimited tables.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-table baseline synthesizer that generates data uniformly at random for each table while preserving table schemas.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The CTGAN Synthesizer uses GAN-based, deep learning methods to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightweight statistical synthesizer that applies simple, column-wise models without learning inter-column dependencies.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Copula GAN Synthesizer uses a mix classic, statistical methods and GAN-based deep learning methods to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Gaussian Copula Synthesizer uses classic, statistical methods to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformer-based deep learning synthesizer that treats tabular data as a sequence modeling problem, inspired by large language models.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The TVAE Synthesizer uses a variational autoencoder (VAE)-based, neural network techniques to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statistical baseline synthesizer that generates values uniformly at random within the observed bounds of each column.
+</t>
   </si>
 </sst>
 </file>
@@ -531,10 +545,10 @@
         <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -560,10 +574,10 @@
         <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3">
         <v>3</v>
@@ -589,10 +603,10 @@
         <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -615,13 +629,13 @@
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -647,10 +661,10 @@
         <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -673,13 +687,13 @@
         <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7">
         <v>4</v>
@@ -705,10 +719,10 @@
         <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8">
         <v>4</v>
@@ -734,10 +748,10 @@
         <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -760,13 +774,13 @@
         <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10">
         <v>2</v>
@@ -792,10 +806,10 @@
         <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -818,13 +832,13 @@
         <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12">
         <v>1</v>

--- a/assets/Model_Details.xlsx
+++ b/assets/Model_Details.xlsx
@@ -14,17 +14,23 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="55">
   <si>
     <t>Synthesizer</t>
   </si>
   <si>
-    <t>Data Type</t>
+    <t>Model Name</t>
+  </si>
+  <si>
+    <t>Data Modality</t>
   </si>
   <si>
     <t>Source</t>
   </si>
   <si>
+    <t>Organization</t>
+  </si>
+  <si>
     <t>Type</t>
   </si>
   <si>
@@ -76,6 +82,39 @@
     <t>UniformSynthesizer</t>
   </si>
   <si>
+    <t>HMA</t>
+  </si>
+  <si>
+    <t>HSA</t>
+  </si>
+  <si>
+    <t>Independent</t>
+  </si>
+  <si>
+    <t>MultiTableUniform</t>
+  </si>
+  <si>
+    <t>CTGAN</t>
+  </si>
+  <si>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>CopulaGAN</t>
+  </si>
+  <si>
+    <t>GaussianCopula</t>
+  </si>
+  <si>
+    <t>RealTabFormer</t>
+  </si>
+  <si>
+    <t>TVAE</t>
+  </si>
+  <si>
+    <t>Uniform</t>
+  </si>
+  <si>
     <t>multi_table</t>
   </si>
   <si>
@@ -89,6 +128,12 @@
   </si>
   <si>
     <t>realtabformer</t>
+  </si>
+  <si>
+    <t>Datacebo</t>
+  </si>
+  <si>
+    <t>World Bank</t>
   </si>
   <si>
     <t>Hierarchical Modeling</t>
@@ -502,10 +547,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -533,323 +578,395 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10">
+        <v>2</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>4</v>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
         <v>20</v>
       </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="B11" t="s">
         <v>31</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="C11" t="s">
         <v>34</v>
       </c>
-      <c r="F7">
-        <v>4</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="D11" t="s">
         <v>35</v>
-      </c>
-      <c r="F8">
-        <v>4</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10">
-        <v>2</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="H10">
-        <v>4</v>
-      </c>
-      <c r="I10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" t="s">
-        <v>28</v>
       </c>
       <c r="E11" t="s">
         <v>38</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" t="s">
+        <v>53</v>
+      </c>
+      <c r="H11">
         <v>5</v>
       </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E12" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
+        <v>38</v>
+      </c>
+      <c r="F12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" t="s">
+        <v>54</v>
       </c>
       <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12" t="b">
         <v>1</v>
       </c>
     </row>

--- a/assets/Model_Details.xlsx
+++ b/assets/Model_Details.xlsx
@@ -888,13 +888,13 @@
         <v>52</v>
       </c>
       <c r="H10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>

--- a/assets/Model_Details.xlsx
+++ b/assets/Model_Details.xlsx
@@ -49,6 +49,27 @@
     <t>On the Pareto Curve</t>
   </si>
   <si>
+    <t>CTGANSynthesizer</t>
+  </si>
+  <si>
+    <t>ColumnSynthesizer</t>
+  </si>
+  <si>
+    <t>CopulaGANSynthesizer</t>
+  </si>
+  <si>
+    <t>GaussianCopulaSynthesizer</t>
+  </si>
+  <si>
+    <t>RealTabFormerSynthesizer</t>
+  </si>
+  <si>
+    <t>TVAESynthesizer</t>
+  </si>
+  <si>
+    <t>UniformSynthesizer</t>
+  </si>
+  <si>
     <t>HMASynthesizer</t>
   </si>
   <si>
@@ -61,25 +82,25 @@
     <t>MultiTableUniformSynthesizer</t>
   </si>
   <si>
-    <t>CTGANSynthesizer</t>
-  </si>
-  <si>
-    <t>ColumnSynthesizer</t>
-  </si>
-  <si>
-    <t>CopulaGANSynthesizer</t>
-  </si>
-  <si>
-    <t>GaussianCopulaSynthesizer</t>
-  </si>
-  <si>
-    <t>RealTabFormerSynthesizer</t>
-  </si>
-  <si>
-    <t>TVAESynthesizer</t>
-  </si>
-  <si>
-    <t>UniformSynthesizer</t>
+    <t>CTGAN</t>
+  </si>
+  <si>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>CopulaGAN</t>
+  </si>
+  <si>
+    <t>GaussianCopula</t>
+  </si>
+  <si>
+    <t>RealTabFormer</t>
+  </si>
+  <si>
+    <t>TVAE</t>
+  </si>
+  <si>
+    <t>Uniform</t>
   </si>
   <si>
     <t>HMA</t>
@@ -94,33 +115,12 @@
     <t>MultiTableUniform</t>
   </si>
   <si>
-    <t>CTGAN</t>
-  </si>
-  <si>
-    <t>Column</t>
-  </si>
-  <si>
-    <t>CopulaGAN</t>
-  </si>
-  <si>
-    <t>GaussianCopula</t>
-  </si>
-  <si>
-    <t>RealTabFormer</t>
-  </si>
-  <si>
-    <t>TVAE</t>
-  </si>
-  <si>
-    <t>Uniform</t>
+    <t>single_table</t>
   </si>
   <si>
     <t>multi_table</t>
   </si>
   <si>
-    <t>single_table</t>
-  </si>
-  <si>
     <t>sdv</t>
   </si>
   <si>
@@ -136,16 +136,44 @@
     <t>World Bank</t>
   </si>
   <si>
+    <t>Deep Learning</t>
+  </si>
+  <si>
+    <t>Statistical</t>
+  </si>
+  <si>
     <t>Hierarchical Modeling</t>
   </si>
   <si>
     <t>Hierarchical Sampling</t>
   </si>
   <si>
-    <t>Statistical</t>
-  </si>
-  <si>
-    <t>Deep Learning</t>
+    <t xml:space="preserve">The CTGAN Synthesizer uses GAN-based, deep learning methods to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightweight statistical synthesizer that applies simple, column-wise models without learning inter-column dependencies.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Copula GAN Synthesizer uses a mix classic, statistical methods and GAN-based deep learning methods to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Gaussian Copula Synthesizer uses classic, statistical methods to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformer-based deep learning synthesizer that treats tabular data as a sequence modeling problem, inspired by large language models.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The TVAE Synthesizer uses a variational autoencoder (VAE)-based, neural network techniques to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statistical baseline synthesizer that generates values uniformly at random within the observed bounds of each column.
+</t>
   </si>
   <si>
     <t xml:space="preserve">The HMA Synthesizer uses hierarchical ML algorithm to learn from real data and generate synthetic data.  The algorithm uses classical statistics.
@@ -161,34 +189,6 @@
   </si>
   <si>
     <t xml:space="preserve">Multi-table baseline synthesizer that generates data uniformly at random for each table while preserving table schemas.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The CTGAN Synthesizer uses GAN-based, deep learning methods to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightweight statistical synthesizer that applies simple, column-wise models without learning inter-column dependencies.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Copula GAN Synthesizer uses a mix classic, statistical methods and GAN-based deep learning methods to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Gaussian Copula Synthesizer uses classic, statistical methods to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformer-based deep learning synthesizer that treats tabular data as a sequence modeling problem, inspired by large language models.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The TVAE Synthesizer uses a variational autoencoder (VAE)-based, neural network techniques to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Statistical baseline synthesizer that generates values uniformly at random within the observed bounds of each column.
 </t>
   </si>
 </sst>
@@ -608,13 +608,13 @@
         <v>44</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="b">
         <v>0</v>
@@ -631,7 +631,7 @@
         <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>38</v>
@@ -643,7 +643,7 @@
         <v>45</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -652,7 +652,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -672,13 +672,13 @@
         <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G4" t="s">
         <v>46</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -701,13 +701,13 @@
         <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
         <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G5" t="s">
         <v>47</v>
@@ -733,16 +733,16 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G6" t="s">
         <v>48</v>
@@ -768,22 +768,22 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
         <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G7" t="s">
         <v>49</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -803,22 +803,22 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
         <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G8" t="s">
         <v>50</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -827,7 +827,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -853,16 +853,16 @@
         <v>51</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -876,10 +876,10 @@
         <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s">
         <v>43</v>
@@ -888,7 +888,7 @@
         <v>52</v>
       </c>
       <c r="H10">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -917,13 +917,13 @@
         <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G11" t="s">
         <v>53</v>
       </c>
       <c r="H11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -952,7 +952,7 @@
         <v>38</v>
       </c>
       <c r="F12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G12" t="s">
         <v>54</v>

--- a/assets/Model_Details.xlsx
+++ b/assets/Model_Details.xlsx
@@ -853,7 +853,7 @@
         <v>51</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I9">
         <v>4</v>
@@ -888,7 +888,7 @@
         <v>52</v>
       </c>
       <c r="H10">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -958,7 +958,7 @@
         <v>54</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12">
         <v>0</v>

--- a/assets/Model_Details.xlsx
+++ b/assets/Model_Details.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="63">
   <si>
     <t>Synthesizer</t>
   </si>
@@ -49,6 +49,21 @@
     <t>On the Pareto Curve</t>
   </si>
   <si>
+    <t>HMASynthesizer</t>
+  </si>
+  <si>
+    <t>HSASynthesizer</t>
+  </si>
+  <si>
+    <t>IndependentSynthesizer</t>
+  </si>
+  <si>
+    <t>MultiTableUniformSynthesizer</t>
+  </si>
+  <si>
+    <t>BootstrapSynthesizer</t>
+  </si>
+  <si>
     <t>CTGANSynthesizer</t>
   </si>
   <si>
@@ -64,22 +79,31 @@
     <t>RealTabFormerSynthesizer</t>
   </si>
   <si>
+    <t>SegmentSynthesizer</t>
+  </si>
+  <si>
     <t>TVAESynthesizer</t>
   </si>
   <si>
     <t>UniformSynthesizer</t>
   </si>
   <si>
-    <t>HMASynthesizer</t>
-  </si>
-  <si>
-    <t>HSASynthesizer</t>
-  </si>
-  <si>
-    <t>IndependentSynthesizer</t>
-  </si>
-  <si>
-    <t>MultiTableUniformSynthesizer</t>
+    <t>XGCSynthesizer</t>
+  </si>
+  <si>
+    <t>HMA</t>
+  </si>
+  <si>
+    <t>HSA</t>
+  </si>
+  <si>
+    <t>Independent</t>
+  </si>
+  <si>
+    <t>MultiTableUniform</t>
+  </si>
+  <si>
+    <t>Bootstrap</t>
   </si>
   <si>
     <t>CTGAN</t>
@@ -97,30 +121,27 @@
     <t>RealTabFormer</t>
   </si>
   <si>
+    <t>Segment</t>
+  </si>
+  <si>
     <t>TVAE</t>
   </si>
   <si>
     <t>Uniform</t>
   </si>
   <si>
-    <t>HMA</t>
-  </si>
-  <si>
-    <t>HSA</t>
-  </si>
-  <si>
-    <t>Independent</t>
-  </si>
-  <si>
-    <t>MultiTableUniform</t>
+    <t>XGC</t>
+  </si>
+  <si>
+    <t>multi_table</t>
+  </si>
+  <si>
+    <t>Unknown</t>
   </si>
   <si>
     <t>single_table</t>
   </si>
   <si>
-    <t>multi_table</t>
-  </si>
-  <si>
     <t>sdv</t>
   </si>
   <si>
@@ -136,16 +157,35 @@
     <t>World Bank</t>
   </si>
   <si>
+    <t>Hierarchical Modeling</t>
+  </si>
+  <si>
+    <t>Hierarchical Sampling</t>
+  </si>
+  <si>
+    <t>Statistical</t>
+  </si>
+  <si>
     <t>Deep Learning</t>
   </si>
   <si>
-    <t>Statistical</t>
-  </si>
-  <si>
-    <t>Hierarchical Modeling</t>
-  </si>
-  <si>
-    <t>Hierarchical Sampling</t>
+    <t xml:space="preserve">The HMA Synthesizer uses hierarchical ML algorithm to learn from real data and generate synthetic data.  The algorithm uses classical statistics.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The HSA Synthesizer uses a segment-based algorithm to learn from your real data and generate synthetic data. This synthesizer offers fast performance for unlimited tables.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Independent Synthesizer learns each table's patterns independently. This synthesizer offers fast performance for unlimited tables.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-table baseline synthesizer that generates data uniformly at random for each table while preserving table schemas.
+</t>
+  </si>
+  <si>
+    <t>No description available.</t>
   </si>
   <si>
     <t xml:space="preserve">The CTGAN Synthesizer uses GAN-based, deep learning methods to train a model and generate synthetic data.
@@ -173,22 +213,6 @@
   </si>
   <si>
     <t xml:space="preserve">Statistical baseline synthesizer that generates values uniformly at random within the observed bounds of each column.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The HMA Synthesizer uses hierarchical ML algorithm to learn from real data and generate synthetic data.  The algorithm uses classical statistics.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The HSA Synthesizer uses a segment-based algorithm to learn from your real data and generate synthetic data. This synthesizer offers fast performance for unlimited tables.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Independent Synthesizer learns each table's patterns independently. This synthesizer offers fast performance for unlimited tables.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-table baseline synthesizer that generates data uniformly at random for each table while preserving table schemas.
 </t>
   </si>
 </sst>
@@ -547,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -590,31 +614,31 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K2" t="b">
         <v>0</v>
@@ -625,25 +649,25 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3">
         <v>38</v>
-      </c>
-      <c r="F3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -660,25 +684,25 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G4" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="H4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -687,7 +711,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -695,25 +719,25 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G5" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -730,25 +754,25 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F6" t="s">
         <v>40</v>
       </c>
       <c r="G6" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -757,7 +781,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -765,25 +789,25 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G7" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -792,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -800,25 +824,25 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G8" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -835,31 +859,31 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F9" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G9" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="H9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -870,25 +894,25 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F10" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G10" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="H10">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -905,25 +929,25 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F11" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G11" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -932,7 +956,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -940,34 +964,139 @@
         <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" t="s">
+        <v>55</v>
+      </c>
+      <c r="H12">
+        <v>8</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
         <v>36</v>
       </c>
-      <c r="E12" t="s">
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13" t="s">
+        <v>61</v>
+      </c>
+      <c r="H13">
+        <v>7</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14" t="s">
+        <v>62</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s">
         <v>38</v>
       </c>
-      <c r="F12" t="s">
-        <v>41</v>
-      </c>
-      <c r="G12" t="s">
-        <v>54</v>
-      </c>
-      <c r="H12">
-        <v>2</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12" t="b">
-        <v>1</v>
+      <c r="C15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" t="s">
+        <v>40</v>
+      </c>
+      <c r="G15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/assets/Model_Details.xlsx
+++ b/assets/Model_Details.xlsx
@@ -49,6 +49,36 @@
     <t>On the Pareto Curve</t>
   </si>
   <si>
+    <t>BootstrapSynthesizer</t>
+  </si>
+  <si>
+    <t>CTGANSynthesizer</t>
+  </si>
+  <si>
+    <t>ColumnSynthesizer</t>
+  </si>
+  <si>
+    <t>CopulaGANSynthesizer</t>
+  </si>
+  <si>
+    <t>GaussianCopulaSynthesizer</t>
+  </si>
+  <si>
+    <t>RealTabFormerSynthesizer</t>
+  </si>
+  <si>
+    <t>SegmentSynthesizer</t>
+  </si>
+  <si>
+    <t>TVAESynthesizer</t>
+  </si>
+  <si>
+    <t>UniformSynthesizer</t>
+  </si>
+  <si>
+    <t>XGCSynthesizer</t>
+  </si>
+  <si>
     <t>HMASynthesizer</t>
   </si>
   <si>
@@ -61,34 +91,34 @@
     <t>MultiTableUniformSynthesizer</t>
   </si>
   <si>
-    <t>BootstrapSynthesizer</t>
-  </si>
-  <si>
-    <t>CTGANSynthesizer</t>
-  </si>
-  <si>
-    <t>ColumnSynthesizer</t>
-  </si>
-  <si>
-    <t>CopulaGANSynthesizer</t>
-  </si>
-  <si>
-    <t>GaussianCopulaSynthesizer</t>
-  </si>
-  <si>
-    <t>RealTabFormerSynthesizer</t>
-  </si>
-  <si>
-    <t>SegmentSynthesizer</t>
-  </si>
-  <si>
-    <t>TVAESynthesizer</t>
-  </si>
-  <si>
-    <t>UniformSynthesizer</t>
-  </si>
-  <si>
-    <t>XGCSynthesizer</t>
+    <t>Bootstrap</t>
+  </si>
+  <si>
+    <t>CTGAN</t>
+  </si>
+  <si>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>CopulaGAN</t>
+  </si>
+  <si>
+    <t>GaussianCopula</t>
+  </si>
+  <si>
+    <t>RealTabFormer</t>
+  </si>
+  <si>
+    <t>Segment</t>
+  </si>
+  <si>
+    <t>TVAE</t>
+  </si>
+  <si>
+    <t>Uniform</t>
+  </si>
+  <si>
+    <t>XGC</t>
   </si>
   <si>
     <t>HMA</t>
@@ -103,45 +133,15 @@
     <t>MultiTableUniform</t>
   </si>
   <si>
-    <t>Bootstrap</t>
-  </si>
-  <si>
-    <t>CTGAN</t>
-  </si>
-  <si>
-    <t>Column</t>
-  </si>
-  <si>
-    <t>CopulaGAN</t>
-  </si>
-  <si>
-    <t>GaussianCopula</t>
-  </si>
-  <si>
-    <t>RealTabFormer</t>
-  </si>
-  <si>
-    <t>Segment</t>
-  </si>
-  <si>
-    <t>TVAE</t>
-  </si>
-  <si>
-    <t>Uniform</t>
-  </si>
-  <si>
-    <t>XGC</t>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>single_table</t>
   </si>
   <si>
     <t>multi_table</t>
   </si>
   <si>
-    <t>Unknown</t>
-  </si>
-  <si>
-    <t>single_table</t>
-  </si>
-  <si>
     <t>sdv</t>
   </si>
   <si>
@@ -157,16 +157,47 @@
     <t>World Bank</t>
   </si>
   <si>
+    <t>Deep Learning</t>
+  </si>
+  <si>
+    <t>Statistical</t>
+  </si>
+  <si>
     <t>Hierarchical Modeling</t>
   </si>
   <si>
     <t>Hierarchical Sampling</t>
   </si>
   <si>
-    <t>Statistical</t>
-  </si>
-  <si>
-    <t>Deep Learning</t>
+    <t>No description available.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The CTGAN Synthesizer uses GAN-based, deep learning methods to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightweight statistical synthesizer that applies simple, column-wise models without learning inter-column dependencies.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Copula GAN Synthesizer uses a mix classic, statistical methods and GAN-based deep learning methods to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Gaussian Copula Synthesizer uses classic, statistical methods to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformer-based deep learning synthesizer that treats tabular data as a sequence modeling problem, inspired by large language models.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The TVAE Synthesizer uses a variational autoencoder (VAE)-based, neural network techniques to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statistical baseline synthesizer that generates values uniformly at random within the observed bounds of each column.
+</t>
   </si>
   <si>
     <t xml:space="preserve">The HMA Synthesizer uses hierarchical ML algorithm to learn from real data and generate synthetic data.  The algorithm uses classical statistics.
@@ -182,37 +213,6 @@
   </si>
   <si>
     <t xml:space="preserve">Multi-table baseline synthesizer that generates data uniformly at random for each table while preserving table schemas.
-</t>
-  </si>
-  <si>
-    <t>No description available.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The CTGAN Synthesizer uses GAN-based, deep learning methods to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightweight statistical synthesizer that applies simple, column-wise models without learning inter-column dependencies.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Copula GAN Synthesizer uses a mix classic, statistical methods and GAN-based deep learning methods to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Gaussian Copula Synthesizer uses classic, statistical methods to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformer-based deep learning synthesizer that treats tabular data as a sequence modeling problem, inspired by large language models.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The TVAE Synthesizer uses a variational autoencoder (VAE)-based, neural network techniques to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Statistical baseline synthesizer that generates values uniformly at random within the observed bounds of each column.
 </t>
   </si>
 </sst>
@@ -623,25 +623,25 @@
         <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G2" t="s">
         <v>51</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -652,7 +652,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
         <v>42</v>
@@ -661,13 +661,13 @@
         <v>45</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G3" t="s">
         <v>52</v>
       </c>
       <c r="H3">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -676,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -687,22 +687,22 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E4" t="s">
         <v>45</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G4" t="s">
         <v>53</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -722,22 +722,22 @@
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
         <v>45</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G5" t="s">
         <v>54</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -746,7 +746,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -763,16 +763,16 @@
         <v>42</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G6" t="s">
         <v>55</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -792,22 +792,22 @@
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G7" t="s">
         <v>56</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -827,22 +827,22 @@
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="G8" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
         <v>42</v>
@@ -871,13 +871,13 @@
         <v>45</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -897,22 +897,22 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s">
         <v>45</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -932,22 +932,22 @@
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E11" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F11" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G11" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="H11">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -967,31 +967,31 @@
         <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
         <v>42</v>
       </c>
       <c r="E12" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F12" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H12">
         <v>8</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1014,10 +1014,10 @@
         <v>50</v>
       </c>
       <c r="G13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H13">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1040,19 +1040,19 @@
         <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E14" t="s">
         <v>45</v>
       </c>
       <c r="F14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1072,19 +1072,19 @@
         <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E15" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F15" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G15" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -1096,7 +1096,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/assets/Model_Details.xlsx
+++ b/assets/Model_Details.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="66">
   <si>
     <t>Synthesizer</t>
   </si>
@@ -64,6 +64,12 @@
     <t>BootstrapSynthesizer</t>
   </si>
   <si>
+    <t>SegmentSynthesizer</t>
+  </si>
+  <si>
+    <t>XGCSynthesizer</t>
+  </si>
+  <si>
     <t>CTGANSynthesizer</t>
   </si>
   <si>
@@ -79,18 +85,12 @@
     <t>RealTabFormerSynthesizer</t>
   </si>
   <si>
-    <t>SegmentSynthesizer</t>
-  </si>
-  <si>
     <t>TVAESynthesizer</t>
   </si>
   <si>
     <t>UniformSynthesizer</t>
   </si>
   <si>
-    <t>XGCSynthesizer</t>
-  </si>
-  <si>
     <t>HMA</t>
   </si>
   <si>
@@ -106,6 +106,12 @@
     <t>Bootstrap</t>
   </si>
   <si>
+    <t>Segment</t>
+  </si>
+  <si>
+    <t>XGC</t>
+  </si>
+  <si>
     <t>CTGAN</t>
   </si>
   <si>
@@ -121,18 +127,12 @@
     <t>RealTabFormer</t>
   </si>
   <si>
-    <t>Segment</t>
-  </si>
-  <si>
     <t>TVAE</t>
   </si>
   <si>
     <t>Uniform</t>
   </si>
   <si>
-    <t>XGC</t>
-  </si>
-  <si>
     <t>multi_table</t>
   </si>
   <si>
@@ -188,6 +188,10 @@
     <t>No description available.</t>
   </si>
   <si>
+    <t xml:space="preserve">The BootstrapSynthesizer is a synthesizer specifically designed to work when you only have a few rows of data. This synthesizer internally bootstraps your real data, and then uses the bootstrapped data to build a model.
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">The CTGAN Synthesizer uses GAN-based, deep learning methods to train a model and generate synthetic data.
 </t>
   </si>
@@ -208,11 +212,19 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">The SegmentSynthesizer calculates different segments of real data, and computes a different model for each one. You can supply any single-table synthesizer for computing the per-segment model. Use this when your real data is highly segmented, containing different patterns for each.
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">The TVAE Synthesizer uses a variational autoencoder (VAE)-based, neural network techniques to train a model and generate synthetic data.
 </t>
   </si>
   <si>
     <t xml:space="preserve">Statistical baseline synthesizer that generates values uniformly at random within the observed bounds of each column.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The XGCSynthesizer stands for eXtraGaussianCopula. It uses classic, statistical methods to train a model and generate synthetic data similar to the GaussianCopulaSynthesizer. However, it contains some additional features for higher quality modeling.
 </t>
   </si>
 </sst>
@@ -571,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -792,22 +804,22 @@
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
         <v>42</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -816,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -827,22 +839,22 @@
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -856,10 +868,10 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
         <v>41</v>
@@ -871,10 +883,10 @@
         <v>45</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -886,15 +898,15 @@
         <v>0</v>
       </c>
       <c r="K9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
         <v>41</v>
@@ -906,13 +918,13 @@
         <v>45</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -926,63 +938,63 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
         <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
         <v>42</v>
       </c>
       <c r="E12" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F12" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H12">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -991,15 +1003,15 @@
         <v>0</v>
       </c>
       <c r="K12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
         <v>41</v>
@@ -1011,13 +1023,13 @@
         <v>45</v>
       </c>
       <c r="F13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1026,76 +1038,181 @@
         <v>0</v>
       </c>
       <c r="K13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
         <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15" t="s">
         <v>42</v>
       </c>
       <c r="E15" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F15" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G15" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H15">
+        <v>7</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" t="s">
+        <v>50</v>
+      </c>
+      <c r="G16" t="s">
+        <v>63</v>
+      </c>
+      <c r="H16">
+        <v>8</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" t="s">
+        <v>45</v>
+      </c>
+      <c r="F17" t="s">
+        <v>49</v>
+      </c>
+      <c r="G17" t="s">
+        <v>64</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" t="s">
+        <v>45</v>
+      </c>
+      <c r="F18" t="s">
+        <v>49</v>
+      </c>
+      <c r="G18" t="s">
+        <v>65</v>
+      </c>
+      <c r="H18">
         <v>5</v>
       </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15" t="b">
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18" t="b">
         <v>1</v>
       </c>
     </row>

--- a/assets/Model_Details.xlsx
+++ b/assets/Model_Details.xlsx
@@ -49,6 +49,36 @@
     <t>On the Pareto Curve</t>
   </si>
   <si>
+    <t>BootstrapSynthesizer</t>
+  </si>
+  <si>
+    <t>SegmentSynthesizer</t>
+  </si>
+  <si>
+    <t>XGCSynthesizer</t>
+  </si>
+  <si>
+    <t>CTGANSynthesizer</t>
+  </si>
+  <si>
+    <t>ColumnSynthesizer</t>
+  </si>
+  <si>
+    <t>CopulaGANSynthesizer</t>
+  </si>
+  <si>
+    <t>GaussianCopulaSynthesizer</t>
+  </si>
+  <si>
+    <t>RealTabFormerSynthesizer</t>
+  </si>
+  <si>
+    <t>TVAESynthesizer</t>
+  </si>
+  <si>
+    <t>UniformSynthesizer</t>
+  </si>
+  <si>
     <t>HMASynthesizer</t>
   </si>
   <si>
@@ -61,34 +91,34 @@
     <t>MultiTableUniformSynthesizer</t>
   </si>
   <si>
-    <t>BootstrapSynthesizer</t>
-  </si>
-  <si>
-    <t>SegmentSynthesizer</t>
-  </si>
-  <si>
-    <t>XGCSynthesizer</t>
-  </si>
-  <si>
-    <t>CTGANSynthesizer</t>
-  </si>
-  <si>
-    <t>ColumnSynthesizer</t>
-  </si>
-  <si>
-    <t>CopulaGANSynthesizer</t>
-  </si>
-  <si>
-    <t>GaussianCopulaSynthesizer</t>
-  </si>
-  <si>
-    <t>RealTabFormerSynthesizer</t>
-  </si>
-  <si>
-    <t>TVAESynthesizer</t>
-  </si>
-  <si>
-    <t>UniformSynthesizer</t>
+    <t>Bootstrap</t>
+  </si>
+  <si>
+    <t>Segment</t>
+  </si>
+  <si>
+    <t>XGC</t>
+  </si>
+  <si>
+    <t>CTGAN</t>
+  </si>
+  <si>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>CopulaGAN</t>
+  </si>
+  <si>
+    <t>GaussianCopula</t>
+  </si>
+  <si>
+    <t>RealTabFormer</t>
+  </si>
+  <si>
+    <t>TVAE</t>
+  </si>
+  <si>
+    <t>Uniform</t>
   </si>
   <si>
     <t>HMA</t>
@@ -103,45 +133,15 @@
     <t>MultiTableUniform</t>
   </si>
   <si>
-    <t>Bootstrap</t>
-  </si>
-  <si>
-    <t>Segment</t>
-  </si>
-  <si>
-    <t>XGC</t>
-  </si>
-  <si>
-    <t>CTGAN</t>
-  </si>
-  <si>
-    <t>Column</t>
-  </si>
-  <si>
-    <t>CopulaGAN</t>
-  </si>
-  <si>
-    <t>GaussianCopula</t>
-  </si>
-  <si>
-    <t>RealTabFormer</t>
-  </si>
-  <si>
-    <t>TVAE</t>
-  </si>
-  <si>
-    <t>Uniform</t>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>single_table</t>
   </si>
   <si>
     <t>multi_table</t>
   </si>
   <si>
-    <t>Unknown</t>
-  </si>
-  <si>
-    <t>single_table</t>
-  </si>
-  <si>
     <t>sdv</t>
   </si>
   <si>
@@ -157,16 +157,59 @@
     <t>World Bank</t>
   </si>
   <si>
+    <t>Statistical</t>
+  </si>
+  <si>
+    <t>Deep Learning</t>
+  </si>
+  <si>
     <t>Hierarchical Modeling</t>
   </si>
   <si>
     <t>Hierarchical Sampling</t>
   </si>
   <si>
-    <t>Statistical</t>
-  </si>
-  <si>
-    <t>Deep Learning</t>
+    <t>No description available.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The BootstrapSynthesizer is a synthesizer specifically designed to work when you only have a few rows of data. This synthesizer internally bootstraps your real data, and then uses the bootstrapped data to build a model.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The CTGAN Synthesizer uses GAN-based, deep learning methods to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightweight statistical synthesizer that applies simple, column-wise models without learning inter-column dependencies.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Copula GAN Synthesizer uses a mix classic, statistical methods and GAN-based deep learning methods to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Gaussian Copula Synthesizer uses classic, statistical methods to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformer-based deep learning synthesizer that treats tabular data as a sequence modeling problem, inspired by large language models.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The SegmentSynthesizer calculates different segments of real data, and computes a different model for each one. You can supply any single-table synthesizer for computing the per-segment model. Use this when your real data is highly segmented, containing different patterns for each.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The TVAE Synthesizer uses a variational autoencoder (VAE)-based, neural network techniques to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statistical baseline synthesizer that generates values uniformly at random within the observed bounds of each column.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The XGCSynthesizer stands for eXtraGaussianCopula. It uses classic, statistical methods to train a model and generate synthetic data similar to the GaussianCopulaSynthesizer. However, it contains some additional features for higher quality modeling.
+</t>
   </si>
   <si>
     <t xml:space="preserve">The HMA Synthesizer uses hierarchical ML algorithm to learn from real data and generate synthetic data.  The algorithm uses classical statistics.
@@ -182,49 +225,6 @@
   </si>
   <si>
     <t xml:space="preserve">Multi-table baseline synthesizer that generates data uniformly at random for each table while preserving table schemas.
-</t>
-  </si>
-  <si>
-    <t>No description available.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The BootstrapSynthesizer is a synthesizer specifically designed to work when you only have a few rows of data. This synthesizer internally bootstraps your real data, and then uses the bootstrapped data to build a model.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The CTGAN Synthesizer uses GAN-based, deep learning methods to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightweight statistical synthesizer that applies simple, column-wise models without learning inter-column dependencies.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Copula GAN Synthesizer uses a mix classic, statistical methods and GAN-based deep learning methods to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Gaussian Copula Synthesizer uses classic, statistical methods to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformer-based deep learning synthesizer that treats tabular data as a sequence modeling problem, inspired by large language models.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The SegmentSynthesizer calculates different segments of real data, and computes a different model for each one. You can supply any single-table synthesizer for computing the per-segment model. Use this when your real data is highly segmented, containing different patterns for each.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The TVAE Synthesizer uses a variational autoencoder (VAE)-based, neural network techniques to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Statistical baseline synthesizer that generates values uniformly at random within the observed bounds of each column.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The XGCSynthesizer stands for eXtraGaussianCopula. It uses classic, statistical methods to train a model and generate synthetic data similar to the GaussianCopulaSynthesizer. However, it contains some additional features for higher quality modeling.
 </t>
   </si>
 </sst>
@@ -635,25 +635,25 @@
         <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G2" t="s">
         <v>51</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -670,16 +670,16 @@
         <v>42</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="G3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H3">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -705,16 +705,16 @@
         <v>42</v>
       </c>
       <c r="E4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="G4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H4">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -728,28 +728,28 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
         <v>45</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -763,10 +763,10 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
         <v>40</v>
@@ -775,16 +775,16 @@
         <v>42</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -793,33 +793,33 @@
         <v>0</v>
       </c>
       <c r="K6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
         <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -833,10 +833,10 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
         <v>40</v>
@@ -845,16 +845,16 @@
         <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G8" t="s">
         <v>55</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -863,18 +863,18 @@
         <v>0</v>
       </c>
       <c r="K8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
         <v>42</v>
@@ -883,13 +883,13 @@
         <v>45</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G9" t="s">
         <v>56</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -898,7 +898,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -909,25 +909,25 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G10" t="s">
         <v>57</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -938,28 +938,28 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E11" t="s">
         <v>45</v>
       </c>
       <c r="F11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G11" t="s">
         <v>58</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -973,13 +973,13 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
         <v>42</v>
@@ -988,13 +988,13 @@
         <v>45</v>
       </c>
       <c r="F12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G12" t="s">
         <v>59</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1003,33 +1003,33 @@
         <v>0</v>
       </c>
       <c r="K12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E13" t="s">
         <v>45</v>
       </c>
       <c r="F13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G13" t="s">
         <v>60</v>
       </c>
       <c r="H13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1038,50 +1038,50 @@
         <v>0</v>
       </c>
       <c r="K13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F14" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G14" t="s">
         <v>61</v>
       </c>
       <c r="H14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
         <v>41</v>
@@ -1099,24 +1099,24 @@
         <v>62</v>
       </c>
       <c r="H15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
         <v>41</v>
@@ -1134,7 +1134,7 @@
         <v>63</v>
       </c>
       <c r="H16">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -1148,28 +1148,28 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
         <v>41</v>
       </c>
       <c r="D17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E17" t="s">
         <v>45</v>
       </c>
       <c r="F17" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G17" t="s">
         <v>64</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1183,28 +1183,28 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
         <v>41</v>
       </c>
       <c r="D18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E18" t="s">
         <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G18" t="s">
         <v>65</v>
       </c>
       <c r="H18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I18">
         <v>0</v>

--- a/assets/Model_Details.xlsx
+++ b/assets/Model_Details.xlsx
@@ -58,6 +58,18 @@
     <t>XGCSynthesizer</t>
   </si>
   <si>
+    <t>HMASynthesizer</t>
+  </si>
+  <si>
+    <t>HSASynthesizer</t>
+  </si>
+  <si>
+    <t>IndependentSynthesizer</t>
+  </si>
+  <si>
+    <t>MultiTableUniformSynthesizer</t>
+  </si>
+  <si>
     <t>CTGANSynthesizer</t>
   </si>
   <si>
@@ -79,18 +91,6 @@
     <t>UniformSynthesizer</t>
   </si>
   <si>
-    <t>HMASynthesizer</t>
-  </si>
-  <si>
-    <t>HSASynthesizer</t>
-  </si>
-  <si>
-    <t>IndependentSynthesizer</t>
-  </si>
-  <si>
-    <t>MultiTableUniformSynthesizer</t>
-  </si>
-  <si>
     <t>Bootstrap</t>
   </si>
   <si>
@@ -100,6 +100,18 @@
     <t>XGC</t>
   </si>
   <si>
+    <t>HMA</t>
+  </si>
+  <si>
+    <t>HSA</t>
+  </si>
+  <si>
+    <t>Independent</t>
+  </si>
+  <si>
+    <t>MultiTableUniform</t>
+  </si>
+  <si>
     <t>CTGAN</t>
   </si>
   <si>
@@ -121,27 +133,15 @@
     <t>Uniform</t>
   </si>
   <si>
-    <t>HMA</t>
-  </si>
-  <si>
-    <t>HSA</t>
-  </si>
-  <si>
-    <t>Independent</t>
-  </si>
-  <si>
-    <t>MultiTableUniform</t>
-  </si>
-  <si>
     <t>Unknown</t>
   </si>
   <si>
+    <t>multi_table</t>
+  </si>
+  <si>
     <t>single_table</t>
   </si>
   <si>
-    <t>multi_table</t>
-  </si>
-  <si>
     <t>sdv</t>
   </si>
   <si>
@@ -157,21 +157,37 @@
     <t>World Bank</t>
   </si>
   <si>
+    <t>Hierarchical Modeling</t>
+  </si>
+  <si>
+    <t>Hierarchical Sampling</t>
+  </si>
+  <si>
     <t>Statistical</t>
   </si>
   <si>
     <t>Deep Learning</t>
   </si>
   <si>
-    <t>Hierarchical Modeling</t>
-  </si>
-  <si>
-    <t>Hierarchical Sampling</t>
-  </si>
-  <si>
     <t>No description available.</t>
   </si>
   <si>
+    <t xml:space="preserve">The HMA Synthesizer uses hierarchical ML algorithm to learn from real data and generate synthetic data.  The algorithm uses classical statistics.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The HSA Synthesizer uses a segment-based algorithm to learn from your real data and generate synthetic data. This synthesizer offers fast performance for unlimited tables.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Independent Synthesizer learns each table's patterns independently. This synthesizer offers fast performance for unlimited tables.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-table baseline synthesizer that generates data uniformly at random for each table while preserving table schemas.
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">The BootstrapSynthesizer is a synthesizer specifically designed to work when you only have a few rows of data. This synthesizer internally bootstraps your real data, and then uses the bootstrapped data to build a model.
 </t>
   </si>
@@ -209,22 +225,6 @@
   </si>
   <si>
     <t xml:space="preserve">The XGCSynthesizer stands for eXtraGaussianCopula. It uses classic, statistical methods to train a model and generate synthetic data similar to the GaussianCopulaSynthesizer. However, it contains some additional features for higher quality modeling.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The HMA Synthesizer uses hierarchical ML algorithm to learn from real data and generate synthetic data.  The algorithm uses classical statistics.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The HSA Synthesizer uses a segment-based algorithm to learn from your real data and generate synthetic data. This synthesizer offers fast performance for unlimited tables.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Independent Synthesizer learns each table's patterns independently. This synthesizer offers fast performance for unlimited tables.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-table baseline synthesizer that generates data uniformly at random for each table while preserving table schemas.
 </t>
   </si>
 </sst>
@@ -728,10 +728,10 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
         <v>40</v>
@@ -749,24 +749,24 @@
         <v>52</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
         <v>40</v>
@@ -784,7 +784,7 @@
         <v>53</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -793,33 +793,33 @@
         <v>0</v>
       </c>
       <c r="K6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
         <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
         <v>45</v>
       </c>
       <c r="F7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G7" t="s">
         <v>54</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -833,28 +833,28 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
         <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
         <v>45</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G8" t="s">
         <v>55</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -863,18 +863,18 @@
         <v>0</v>
       </c>
       <c r="K8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
         <v>42</v>
@@ -883,13 +883,13 @@
         <v>45</v>
       </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G9" t="s">
         <v>56</v>
       </c>
       <c r="H9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -898,7 +898,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -909,25 +909,25 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G10" t="s">
         <v>57</v>
       </c>
       <c r="H10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -938,28 +938,28 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E11" t="s">
         <v>45</v>
       </c>
       <c r="F11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G11" t="s">
         <v>58</v>
       </c>
       <c r="H11">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -973,13 +973,13 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
         <v>42</v>
@@ -988,13 +988,13 @@
         <v>45</v>
       </c>
       <c r="F12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G12" t="s">
         <v>59</v>
       </c>
       <c r="H12">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1003,33 +1003,33 @@
         <v>0</v>
       </c>
       <c r="K12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E13" t="s">
         <v>45</v>
       </c>
       <c r="F13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G13" t="s">
         <v>60</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1043,22 +1043,22 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F14" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G14" t="s">
         <v>61</v>
@@ -1067,21 +1067,21 @@
         <v>5</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s">
         <v>41</v>
@@ -1099,24 +1099,24 @@
         <v>62</v>
       </c>
       <c r="H15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
         <v>41</v>
@@ -1134,7 +1134,7 @@
         <v>63</v>
       </c>
       <c r="H16">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -1148,28 +1148,28 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
         <v>41</v>
       </c>
       <c r="D17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E17" t="s">
         <v>45</v>
       </c>
       <c r="F17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G17" t="s">
         <v>64</v>
       </c>
       <c r="H17">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1183,28 +1183,28 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
         <v>41</v>
       </c>
       <c r="D18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E18" t="s">
         <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G18" t="s">
         <v>65</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/assets/Model_Details.xlsx
+++ b/assets/Model_Details.xlsx
@@ -58,6 +58,27 @@
     <t>XGCSynthesizer</t>
   </si>
   <si>
+    <t>CTGANSynthesizer</t>
+  </si>
+  <si>
+    <t>ColumnSynthesizer</t>
+  </si>
+  <si>
+    <t>CopulaGANSynthesizer</t>
+  </si>
+  <si>
+    <t>GaussianCopulaSynthesizer</t>
+  </si>
+  <si>
+    <t>RealTabFormerSynthesizer</t>
+  </si>
+  <si>
+    <t>TVAESynthesizer</t>
+  </si>
+  <si>
+    <t>UniformSynthesizer</t>
+  </si>
+  <si>
     <t>HMASynthesizer</t>
   </si>
   <si>
@@ -70,27 +91,6 @@
     <t>MultiTableUniformSynthesizer</t>
   </si>
   <si>
-    <t>CTGANSynthesizer</t>
-  </si>
-  <si>
-    <t>ColumnSynthesizer</t>
-  </si>
-  <si>
-    <t>CopulaGANSynthesizer</t>
-  </si>
-  <si>
-    <t>GaussianCopulaSynthesizer</t>
-  </si>
-  <si>
-    <t>RealTabFormerSynthesizer</t>
-  </si>
-  <si>
-    <t>TVAESynthesizer</t>
-  </si>
-  <si>
-    <t>UniformSynthesizer</t>
-  </si>
-  <si>
     <t>Bootstrap</t>
   </si>
   <si>
@@ -100,6 +100,27 @@
     <t>XGC</t>
   </si>
   <si>
+    <t>CTGAN</t>
+  </si>
+  <si>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>CopulaGAN</t>
+  </si>
+  <si>
+    <t>GaussianCopula</t>
+  </si>
+  <si>
+    <t>RealTabFormer</t>
+  </si>
+  <si>
+    <t>TVAE</t>
+  </si>
+  <si>
+    <t>Uniform</t>
+  </si>
+  <si>
     <t>HMA</t>
   </si>
   <si>
@@ -112,36 +133,15 @@
     <t>MultiTableUniform</t>
   </si>
   <si>
-    <t>CTGAN</t>
-  </si>
-  <si>
-    <t>Column</t>
-  </si>
-  <si>
-    <t>CopulaGAN</t>
-  </si>
-  <si>
-    <t>GaussianCopula</t>
-  </si>
-  <si>
-    <t>RealTabFormer</t>
-  </si>
-  <si>
-    <t>TVAE</t>
-  </si>
-  <si>
-    <t>Uniform</t>
-  </si>
-  <si>
     <t>Unknown</t>
   </si>
   <si>
+    <t>single_table</t>
+  </si>
+  <si>
     <t>multi_table</t>
   </si>
   <si>
-    <t>single_table</t>
-  </si>
-  <si>
     <t>sdv</t>
   </si>
   <si>
@@ -157,21 +157,61 @@
     <t>World Bank</t>
   </si>
   <si>
+    <t>Statistical</t>
+  </si>
+  <si>
+    <t>Deep Learning</t>
+  </si>
+  <si>
     <t>Hierarchical Modeling</t>
   </si>
   <si>
     <t>Hierarchical Sampling</t>
   </si>
   <si>
-    <t>Statistical</t>
-  </si>
-  <si>
-    <t>Deep Learning</t>
-  </si>
-  <si>
     <t>No description available.</t>
   </si>
   <si>
+    <t xml:space="preserve">The BootstrapSynthesizer is a synthesizer specifically designed to work when you only have a few rows of data. This synthesizer internally bootstraps your real data, and then uses the bootstrapped data to build a model.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The CTGAN Synthesizer uses GAN-based, deep learning methods to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightweight statistical synthesizer that applies simple, column-wise models without learning inter-column dependencies.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Copula GAN Synthesizer uses a mix classic, statistical methods and GAN-based deep learning methods to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Gaussian Copula Synthesizer uses classic, statistical methods to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformer-based deep learning synthesizer that treats tabular data as a sequence modeling problem, inspired by large language models.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The SegmentSynthesizer calculates different segments of real data, and computes a different model for each one. You can supply any single-table synthesizer for computing the per-segment model. Use this when your real data is highly segmented, containing different patterns for each.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The TVAE Synthesizer uses a variational autoencoder (VAE)-based, neural network techniques to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statistical baseline synthesizer that generates values uniformly at random within the observed bounds of each column.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The XGCSynthesizer stands for eXtraGaussianCopula. It uses classic, statistical methods to train a model and generate synthetic data similar to the GaussianCopulaSynthesizer. However, it contains some additional features for higher quality modeling.
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">The HMA Synthesizer uses hierarchical ML algorithm to learn from real data and generate synthetic data.  The algorithm uses classical statistics.
 </t>
   </si>
@@ -185,46 +225,6 @@
   </si>
   <si>
     <t xml:space="preserve">Multi-table baseline synthesizer that generates data uniformly at random for each table while preserving table schemas.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The BootstrapSynthesizer is a synthesizer specifically designed to work when you only have a few rows of data. This synthesizer internally bootstraps your real data, and then uses the bootstrapped data to build a model.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The CTGAN Synthesizer uses GAN-based, deep learning methods to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightweight statistical synthesizer that applies simple, column-wise models without learning inter-column dependencies.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Copula GAN Synthesizer uses a mix classic, statistical methods and GAN-based deep learning methods to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Gaussian Copula Synthesizer uses classic, statistical methods to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformer-based deep learning synthesizer that treats tabular data as a sequence modeling problem, inspired by large language models.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The SegmentSynthesizer calculates different segments of real data, and computes a different model for each one. You can supply any single-table synthesizer for computing the per-segment model. Use this when your real data is highly segmented, containing different patterns for each.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The TVAE Synthesizer uses a variational autoencoder (VAE)-based, neural network techniques to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Statistical baseline synthesizer that generates values uniformly at random within the observed bounds of each column.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The XGCSynthesizer stands for eXtraGaussianCopula. It uses classic, statistical methods to train a model and generate synthetic data similar to the GaussianCopulaSynthesizer. However, it contains some additional features for higher quality modeling.
 </t>
   </si>
 </sst>
@@ -728,10 +728,10 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
         <v>40</v>
@@ -749,24 +749,24 @@
         <v>52</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
         <v>40</v>
@@ -784,7 +784,7 @@
         <v>53</v>
       </c>
       <c r="H6">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -793,33 +793,33 @@
         <v>0</v>
       </c>
       <c r="K6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
         <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
         <v>45</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G7" t="s">
         <v>54</v>
       </c>
       <c r="H7">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -833,28 +833,28 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
         <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
         <v>45</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G8" t="s">
         <v>55</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -863,18 +863,18 @@
         <v>0</v>
       </c>
       <c r="K8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
         <v>42</v>
@@ -883,13 +883,13 @@
         <v>45</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G9" t="s">
         <v>56</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -909,25 +909,25 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G10" t="s">
         <v>57</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -938,28 +938,28 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E11" t="s">
         <v>45</v>
       </c>
       <c r="F11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G11" t="s">
         <v>58</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -973,13 +973,13 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
         <v>42</v>
@@ -988,13 +988,13 @@
         <v>45</v>
       </c>
       <c r="F12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G12" t="s">
         <v>59</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1003,33 +1003,33 @@
         <v>0</v>
       </c>
       <c r="K12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E13" t="s">
         <v>45</v>
       </c>
       <c r="F13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G13" t="s">
         <v>60</v>
       </c>
       <c r="H13">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1043,22 +1043,22 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F14" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G14" t="s">
         <v>61</v>
@@ -1067,7 +1067,7 @@
         <v>5</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
         <v>41</v>
@@ -1099,24 +1099,24 @@
         <v>62</v>
       </c>
       <c r="H15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
         <v>41</v>
@@ -1134,13 +1134,13 @@
         <v>63</v>
       </c>
       <c r="H16">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
@@ -1148,34 +1148,34 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
         <v>41</v>
       </c>
       <c r="D17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E17" t="s">
         <v>45</v>
       </c>
       <c r="F17" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G17" t="s">
         <v>64</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
@@ -1183,37 +1183,37 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
         <v>41</v>
       </c>
       <c r="D18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E18" t="s">
         <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G18" t="s">
         <v>65</v>
       </c>
       <c r="H18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/assets/Model_Details.xlsx
+++ b/assets/Model_Details.xlsx
@@ -58,6 +58,18 @@
     <t>XGCSynthesizer</t>
   </si>
   <si>
+    <t>HMASynthesizer</t>
+  </si>
+  <si>
+    <t>HSASynthesizer</t>
+  </si>
+  <si>
+    <t>IndependentSynthesizer</t>
+  </si>
+  <si>
+    <t>MultiTableUniformSynthesizer</t>
+  </si>
+  <si>
     <t>CTGANSynthesizer</t>
   </si>
   <si>
@@ -79,18 +91,6 @@
     <t>UniformSynthesizer</t>
   </si>
   <si>
-    <t>HMASynthesizer</t>
-  </si>
-  <si>
-    <t>HSASynthesizer</t>
-  </si>
-  <si>
-    <t>IndependentSynthesizer</t>
-  </si>
-  <si>
-    <t>MultiTableUniformSynthesizer</t>
-  </si>
-  <si>
     <t>Bootstrap</t>
   </si>
   <si>
@@ -100,6 +100,18 @@
     <t>XGC</t>
   </si>
   <si>
+    <t>HMA</t>
+  </si>
+  <si>
+    <t>HSA</t>
+  </si>
+  <si>
+    <t>Independent</t>
+  </si>
+  <si>
+    <t>MultiTableUniform</t>
+  </si>
+  <si>
     <t>CTGAN</t>
   </si>
   <si>
@@ -121,27 +133,15 @@
     <t>Uniform</t>
   </si>
   <si>
-    <t>HMA</t>
-  </si>
-  <si>
-    <t>HSA</t>
-  </si>
-  <si>
-    <t>Independent</t>
-  </si>
-  <si>
-    <t>MultiTableUniform</t>
-  </si>
-  <si>
     <t>Unknown</t>
   </si>
   <si>
+    <t>multi_table</t>
+  </si>
+  <si>
     <t>single_table</t>
   </si>
   <si>
-    <t>multi_table</t>
-  </si>
-  <si>
     <t>sdv</t>
   </si>
   <si>
@@ -157,21 +157,37 @@
     <t>World Bank</t>
   </si>
   <si>
+    <t>Hierarchical Modeling</t>
+  </si>
+  <si>
+    <t>Hierarchical Sampling</t>
+  </si>
+  <si>
     <t>Statistical</t>
   </si>
   <si>
     <t>Deep Learning</t>
   </si>
   <si>
-    <t>Hierarchical Modeling</t>
-  </si>
-  <si>
-    <t>Hierarchical Sampling</t>
-  </si>
-  <si>
     <t>No description available.</t>
   </si>
   <si>
+    <t xml:space="preserve">The HMA Synthesizer uses hierarchical ML algorithm to learn from real data and generate synthetic data.  The algorithm uses classical statistics.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The HSA Synthesizer uses a segment-based algorithm to learn from your real data and generate synthetic data. This synthesizer offers fast performance for unlimited tables.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Independent Synthesizer learns each table's patterns independently. This synthesizer offers fast performance for unlimited tables.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-table baseline synthesizer that generates data uniformly at random for each table while preserving table schemas.
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">The BootstrapSynthesizer is a synthesizer specifically designed to work when you only have a few rows of data. This synthesizer internally bootstraps your real data, and then uses the bootstrapped data to build a model.
 </t>
   </si>
@@ -209,22 +225,6 @@
   </si>
   <si>
     <t xml:space="preserve">The XGCSynthesizer stands for eXtraGaussianCopula. It uses classic, statistical methods to train a model and generate synthetic data similar to the GaussianCopulaSynthesizer. However, it contains some additional features for higher quality modeling.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The HMA Synthesizer uses hierarchical ML algorithm to learn from real data and generate synthetic data.  The algorithm uses classical statistics.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The HSA Synthesizer uses a segment-based algorithm to learn from your real data and generate synthetic data. This synthesizer offers fast performance for unlimited tables.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Independent Synthesizer learns each table's patterns independently. This synthesizer offers fast performance for unlimited tables.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-table baseline synthesizer that generates data uniformly at random for each table while preserving table schemas.
 </t>
   </si>
 </sst>
@@ -728,10 +728,10 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
         <v>40</v>
@@ -749,24 +749,24 @@
         <v>52</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
         <v>40</v>
@@ -784,48 +784,48 @@
         <v>53</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
         <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
         <v>45</v>
       </c>
       <c r="F7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G7" t="s">
         <v>54</v>
       </c>
       <c r="H7">
+        <v>61</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
         <v>2</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
@@ -833,48 +833,48 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
         <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
         <v>45</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G8" t="s">
         <v>55</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
         <v>42</v>
@@ -883,13 +883,13 @@
         <v>45</v>
       </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G9" t="s">
         <v>56</v>
       </c>
       <c r="H9">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -909,25 +909,25 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G10" t="s">
         <v>57</v>
       </c>
       <c r="H10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -938,28 +938,28 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E11" t="s">
         <v>45</v>
       </c>
       <c r="F11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G11" t="s">
         <v>58</v>
       </c>
       <c r="H11">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -973,13 +973,13 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
         <v>42</v>
@@ -988,13 +988,13 @@
         <v>45</v>
       </c>
       <c r="F12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G12" t="s">
         <v>59</v>
       </c>
       <c r="H12">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1003,33 +1003,33 @@
         <v>0</v>
       </c>
       <c r="K12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E13" t="s">
         <v>45</v>
       </c>
       <c r="F13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G13" t="s">
         <v>60</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1043,31 +1043,31 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F14" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G14" t="s">
         <v>61</v>
       </c>
       <c r="H14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s">
         <v>41</v>
@@ -1099,24 +1099,24 @@
         <v>62</v>
       </c>
       <c r="H15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I15">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
         <v>41</v>
@@ -1134,13 +1134,13 @@
         <v>63</v>
       </c>
       <c r="H16">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
@@ -1148,34 +1148,34 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
         <v>41</v>
       </c>
       <c r="D17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E17" t="s">
         <v>45</v>
       </c>
       <c r="F17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G17" t="s">
         <v>64</v>
       </c>
       <c r="H17">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
@@ -1183,34 +1183,34 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
         <v>41</v>
       </c>
       <c r="D18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E18" t="s">
         <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G18" t="s">
         <v>65</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K18" t="b">
         <v>1</v>

--- a/assets/Model_Details.xlsx
+++ b/assets/Model_Details.xlsx
@@ -58,6 +58,27 @@
     <t>XGCSynthesizer</t>
   </si>
   <si>
+    <t>CTGANSynthesizer</t>
+  </si>
+  <si>
+    <t>ColumnSynthesizer</t>
+  </si>
+  <si>
+    <t>CopulaGANSynthesizer</t>
+  </si>
+  <si>
+    <t>GaussianCopulaSynthesizer</t>
+  </si>
+  <si>
+    <t>RealTabFormerSynthesizer</t>
+  </si>
+  <si>
+    <t>TVAESynthesizer</t>
+  </si>
+  <si>
+    <t>UniformSynthesizer</t>
+  </si>
+  <si>
     <t>HMASynthesizer</t>
   </si>
   <si>
@@ -70,27 +91,6 @@
     <t>MultiTableUniformSynthesizer</t>
   </si>
   <si>
-    <t>CTGANSynthesizer</t>
-  </si>
-  <si>
-    <t>ColumnSynthesizer</t>
-  </si>
-  <si>
-    <t>CopulaGANSynthesizer</t>
-  </si>
-  <si>
-    <t>GaussianCopulaSynthesizer</t>
-  </si>
-  <si>
-    <t>RealTabFormerSynthesizer</t>
-  </si>
-  <si>
-    <t>TVAESynthesizer</t>
-  </si>
-  <si>
-    <t>UniformSynthesizer</t>
-  </si>
-  <si>
     <t>Bootstrap</t>
   </si>
   <si>
@@ -100,6 +100,27 @@
     <t>XGC</t>
   </si>
   <si>
+    <t>CTGAN</t>
+  </si>
+  <si>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>CopulaGAN</t>
+  </si>
+  <si>
+    <t>GaussianCopula</t>
+  </si>
+  <si>
+    <t>RealTabFormer</t>
+  </si>
+  <si>
+    <t>TVAE</t>
+  </si>
+  <si>
+    <t>Uniform</t>
+  </si>
+  <si>
     <t>HMA</t>
   </si>
   <si>
@@ -112,36 +133,15 @@
     <t>MultiTableUniform</t>
   </si>
   <si>
-    <t>CTGAN</t>
-  </si>
-  <si>
-    <t>Column</t>
-  </si>
-  <si>
-    <t>CopulaGAN</t>
-  </si>
-  <si>
-    <t>GaussianCopula</t>
-  </si>
-  <si>
-    <t>RealTabFormer</t>
-  </si>
-  <si>
-    <t>TVAE</t>
-  </si>
-  <si>
-    <t>Uniform</t>
-  </si>
-  <si>
     <t>Unknown</t>
   </si>
   <si>
+    <t>single_table</t>
+  </si>
+  <si>
     <t>multi_table</t>
   </si>
   <si>
-    <t>single_table</t>
-  </si>
-  <si>
     <t>sdv</t>
   </si>
   <si>
@@ -157,21 +157,61 @@
     <t>World Bank</t>
   </si>
   <si>
+    <t>Statistical</t>
+  </si>
+  <si>
+    <t>Deep Learning</t>
+  </si>
+  <si>
     <t>Hierarchical Modeling</t>
   </si>
   <si>
     <t>Hierarchical Sampling</t>
   </si>
   <si>
-    <t>Statistical</t>
-  </si>
-  <si>
-    <t>Deep Learning</t>
-  </si>
-  <si>
     <t>No description available.</t>
   </si>
   <si>
+    <t xml:space="preserve">The BootstrapSynthesizer is a synthesizer specifically designed to work when you only have a few rows of data. This synthesizer internally bootstraps your real data, and then uses the bootstrapped data to build a model.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The CTGAN Synthesizer uses GAN-based, deep learning methods to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightweight statistical synthesizer that applies simple, column-wise models without learning inter-column dependencies.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Copula GAN Synthesizer uses a mix classic, statistical methods and GAN-based deep learning methods to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Gaussian Copula Synthesizer uses classic, statistical methods to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformer-based deep learning synthesizer that treats tabular data as a sequence modeling problem, inspired by large language models.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The SegmentSynthesizer calculates different segments of real data, and computes a different model for each one. You can supply any single-table synthesizer for computing the per-segment model. Use this when your real data is highly segmented, containing different patterns for each.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The TVAE Synthesizer uses a variational autoencoder (VAE)-based, neural network techniques to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statistical baseline synthesizer that generates values uniformly at random within the observed bounds of each column.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The XGCSynthesizer stands for eXtraGaussianCopula. It uses classic, statistical methods to train a model and generate synthetic data similar to the GaussianCopulaSynthesizer. However, it contains some additional features for higher quality modeling.
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">The HMA Synthesizer uses hierarchical ML algorithm to learn from real data and generate synthetic data.  The algorithm uses classical statistics.
 </t>
   </si>
@@ -185,46 +225,6 @@
   </si>
   <si>
     <t xml:space="preserve">Multi-table baseline synthesizer that generates data uniformly at random for each table while preserving table schemas.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The BootstrapSynthesizer is a synthesizer specifically designed to work when you only have a few rows of data. This synthesizer internally bootstraps your real data, and then uses the bootstrapped data to build a model.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The CTGAN Synthesizer uses GAN-based, deep learning methods to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightweight statistical synthesizer that applies simple, column-wise models without learning inter-column dependencies.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Copula GAN Synthesizer uses a mix classic, statistical methods and GAN-based deep learning methods to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Gaussian Copula Synthesizer uses classic, statistical methods to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformer-based deep learning synthesizer that treats tabular data as a sequence modeling problem, inspired by large language models.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The SegmentSynthesizer calculates different segments of real data, and computes a different model for each one. You can supply any single-table synthesizer for computing the per-segment model. Use this when your real data is highly segmented, containing different patterns for each.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The TVAE Synthesizer uses a variational autoencoder (VAE)-based, neural network techniques to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Statistical baseline synthesizer that generates values uniformly at random within the observed bounds of each column.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The XGCSynthesizer stands for eXtraGaussianCopula. It uses classic, statistical methods to train a model and generate synthetic data similar to the GaussianCopulaSynthesizer. However, it contains some additional features for higher quality modeling.
 </t>
   </si>
 </sst>
@@ -728,10 +728,10 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
         <v>40</v>
@@ -749,24 +749,24 @@
         <v>52</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
         <v>40</v>
@@ -784,48 +784,48 @@
         <v>53</v>
       </c>
       <c r="H6">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
         <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
         <v>45</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G7" t="s">
         <v>54</v>
       </c>
       <c r="H7">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
         <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
         <v>45</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G8" t="s">
         <v>55</v>
@@ -860,21 +860,21 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
         <v>42</v>
@@ -883,13 +883,13 @@
         <v>45</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G9" t="s">
         <v>56</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -909,25 +909,25 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G10" t="s">
         <v>57</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -938,28 +938,28 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E11" t="s">
         <v>45</v>
       </c>
       <c r="F11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G11" t="s">
         <v>58</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -973,13 +973,13 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
         <v>42</v>
@@ -988,13 +988,13 @@
         <v>45</v>
       </c>
       <c r="F12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G12" t="s">
         <v>59</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1003,33 +1003,33 @@
         <v>0</v>
       </c>
       <c r="K12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E13" t="s">
         <v>45</v>
       </c>
       <c r="F13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G13" t="s">
         <v>60</v>
       </c>
       <c r="H13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1043,45 +1043,45 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F14" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G14" t="s">
         <v>61</v>
       </c>
       <c r="H14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
         <v>41</v>
@@ -1099,24 +1099,24 @@
         <v>62</v>
       </c>
       <c r="H15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
         <v>41</v>
@@ -1134,13 +1134,13 @@
         <v>63</v>
       </c>
       <c r="H16">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
@@ -1148,34 +1148,34 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
         <v>41</v>
       </c>
       <c r="D17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E17" t="s">
         <v>45</v>
       </c>
       <c r="F17" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G17" t="s">
         <v>64</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
@@ -1183,37 +1183,37 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
         <v>41</v>
       </c>
       <c r="D18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E18" t="s">
         <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G18" t="s">
         <v>65</v>
       </c>
       <c r="H18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/assets/Model_Details.xlsx
+++ b/assets/Model_Details.xlsx
@@ -58,6 +58,18 @@
     <t>XGCSynthesizer</t>
   </si>
   <si>
+    <t>HMASynthesizer</t>
+  </si>
+  <si>
+    <t>HSASynthesizer</t>
+  </si>
+  <si>
+    <t>IndependentSynthesizer</t>
+  </si>
+  <si>
+    <t>MultiTableUniformSynthesizer</t>
+  </si>
+  <si>
     <t>CTGANSynthesizer</t>
   </si>
   <si>
@@ -79,18 +91,6 @@
     <t>UniformSynthesizer</t>
   </si>
   <si>
-    <t>HMASynthesizer</t>
-  </si>
-  <si>
-    <t>HSASynthesizer</t>
-  </si>
-  <si>
-    <t>IndependentSynthesizer</t>
-  </si>
-  <si>
-    <t>MultiTableUniformSynthesizer</t>
-  </si>
-  <si>
     <t>Bootstrap</t>
   </si>
   <si>
@@ -100,6 +100,18 @@
     <t>XGC</t>
   </si>
   <si>
+    <t>HMA</t>
+  </si>
+  <si>
+    <t>HSA</t>
+  </si>
+  <si>
+    <t>Independent</t>
+  </si>
+  <si>
+    <t>MultiTableUniform</t>
+  </si>
+  <si>
     <t>CTGAN</t>
   </si>
   <si>
@@ -121,27 +133,15 @@
     <t>Uniform</t>
   </si>
   <si>
-    <t>HMA</t>
-  </si>
-  <si>
-    <t>HSA</t>
-  </si>
-  <si>
-    <t>Independent</t>
-  </si>
-  <si>
-    <t>MultiTableUniform</t>
-  </si>
-  <si>
     <t>Unknown</t>
   </si>
   <si>
+    <t>multi_table</t>
+  </si>
+  <si>
     <t>single_table</t>
   </si>
   <si>
-    <t>multi_table</t>
-  </si>
-  <si>
     <t>sdv</t>
   </si>
   <si>
@@ -157,21 +157,37 @@
     <t>World Bank</t>
   </si>
   <si>
+    <t>Hierarchical Modeling</t>
+  </si>
+  <si>
+    <t>Hierarchical Sampling</t>
+  </si>
+  <si>
     <t>Statistical</t>
   </si>
   <si>
     <t>Deep Learning</t>
   </si>
   <si>
-    <t>Hierarchical Modeling</t>
-  </si>
-  <si>
-    <t>Hierarchical Sampling</t>
-  </si>
-  <si>
     <t>No description available.</t>
   </si>
   <si>
+    <t xml:space="preserve">The HMA Synthesizer uses hierarchical ML algorithm to learn from real data and generate synthetic data.  The algorithm uses classical statistics.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The HSA Synthesizer uses a segment-based algorithm to learn from your real data and generate synthetic data. This synthesizer offers fast performance for unlimited tables.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Independent Synthesizer learns each table's patterns independently. This synthesizer offers fast performance for unlimited tables.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-table baseline synthesizer that generates data uniformly at random for each table while preserving table schemas.
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">The BootstrapSynthesizer is a synthesizer specifically designed to work when you only have a few rows of data. This synthesizer internally bootstraps your real data, and then uses the bootstrapped data to build a model.
 </t>
   </si>
@@ -209,22 +225,6 @@
   </si>
   <si>
     <t xml:space="preserve">The XGCSynthesizer stands for eXtraGaussianCopula. It uses classic, statistical methods to train a model and generate synthetic data similar to the GaussianCopulaSynthesizer. However, it contains some additional features for higher quality modeling.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The HMA Synthesizer uses hierarchical ML algorithm to learn from real data and generate synthetic data.  The algorithm uses classical statistics.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The HSA Synthesizer uses a segment-based algorithm to learn from your real data and generate synthetic data. This synthesizer offers fast performance for unlimited tables.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Independent Synthesizer learns each table's patterns independently. This synthesizer offers fast performance for unlimited tables.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-table baseline synthesizer that generates data uniformly at random for each table while preserving table schemas.
 </t>
   </si>
 </sst>
@@ -728,10 +728,10 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
         <v>40</v>
@@ -749,24 +749,24 @@
         <v>52</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
         <v>40</v>
@@ -784,48 +784,48 @@
         <v>53</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
         <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
         <v>45</v>
       </c>
       <c r="F7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G7" t="s">
         <v>54</v>
       </c>
       <c r="H7">
+        <v>59</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
         <v>2</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
         <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
         <v>45</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G8" t="s">
         <v>55</v>
@@ -860,7 +860,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
@@ -868,13 +868,13 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
         <v>42</v>
@@ -883,13 +883,13 @@
         <v>45</v>
       </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G9" t="s">
         <v>56</v>
       </c>
       <c r="H9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -909,25 +909,25 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G10" t="s">
         <v>57</v>
       </c>
       <c r="H10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -938,28 +938,28 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E11" t="s">
         <v>45</v>
       </c>
       <c r="F11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G11" t="s">
         <v>58</v>
       </c>
       <c r="H11">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -973,13 +973,13 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
         <v>42</v>
@@ -988,13 +988,13 @@
         <v>45</v>
       </c>
       <c r="F12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G12" t="s">
         <v>59</v>
       </c>
       <c r="H12">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1003,33 +1003,33 @@
         <v>0</v>
       </c>
       <c r="K12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E13" t="s">
         <v>45</v>
       </c>
       <c r="F13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G13" t="s">
         <v>60</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1043,28 +1043,28 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F14" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G14" t="s">
         <v>61</v>
       </c>
       <c r="H14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1073,15 +1073,15 @@
         <v>0</v>
       </c>
       <c r="K14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s">
         <v>41</v>
@@ -1099,24 +1099,24 @@
         <v>62</v>
       </c>
       <c r="H15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I15">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
         <v>41</v>
@@ -1134,13 +1134,13 @@
         <v>63</v>
       </c>
       <c r="H16">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
@@ -1148,34 +1148,34 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
         <v>41</v>
       </c>
       <c r="D17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E17" t="s">
         <v>45</v>
       </c>
       <c r="F17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G17" t="s">
         <v>64</v>
       </c>
       <c r="H17">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
@@ -1183,37 +1183,37 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
         <v>41</v>
       </c>
       <c r="D18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E18" t="s">
         <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G18" t="s">
         <v>65</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/assets/Model_Details.xlsx
+++ b/assets/Model_Details.xlsx
@@ -58,6 +58,27 @@
     <t>XGCSynthesizer</t>
   </si>
   <si>
+    <t>CTGANSynthesizer</t>
+  </si>
+  <si>
+    <t>ColumnSynthesizer</t>
+  </si>
+  <si>
+    <t>CopulaGANSynthesizer</t>
+  </si>
+  <si>
+    <t>GaussianCopulaSynthesizer</t>
+  </si>
+  <si>
+    <t>RealTabFormerSynthesizer</t>
+  </si>
+  <si>
+    <t>TVAESynthesizer</t>
+  </si>
+  <si>
+    <t>UniformSynthesizer</t>
+  </si>
+  <si>
     <t>HMASynthesizer</t>
   </si>
   <si>
@@ -70,27 +91,6 @@
     <t>MultiTableUniformSynthesizer</t>
   </si>
   <si>
-    <t>CTGANSynthesizer</t>
-  </si>
-  <si>
-    <t>ColumnSynthesizer</t>
-  </si>
-  <si>
-    <t>CopulaGANSynthesizer</t>
-  </si>
-  <si>
-    <t>GaussianCopulaSynthesizer</t>
-  </si>
-  <si>
-    <t>RealTabFormerSynthesizer</t>
-  </si>
-  <si>
-    <t>TVAESynthesizer</t>
-  </si>
-  <si>
-    <t>UniformSynthesizer</t>
-  </si>
-  <si>
     <t>Bootstrap</t>
   </si>
   <si>
@@ -100,6 +100,27 @@
     <t>XGC</t>
   </si>
   <si>
+    <t>CTGAN</t>
+  </si>
+  <si>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>CopulaGAN</t>
+  </si>
+  <si>
+    <t>GaussianCopula</t>
+  </si>
+  <si>
+    <t>RealTabFormer</t>
+  </si>
+  <si>
+    <t>TVAE</t>
+  </si>
+  <si>
+    <t>Uniform</t>
+  </si>
+  <si>
     <t>HMA</t>
   </si>
   <si>
@@ -112,36 +133,15 @@
     <t>MultiTableUniform</t>
   </si>
   <si>
-    <t>CTGAN</t>
-  </si>
-  <si>
-    <t>Column</t>
-  </si>
-  <si>
-    <t>CopulaGAN</t>
-  </si>
-  <si>
-    <t>GaussianCopula</t>
-  </si>
-  <si>
-    <t>RealTabFormer</t>
-  </si>
-  <si>
-    <t>TVAE</t>
-  </si>
-  <si>
-    <t>Uniform</t>
-  </si>
-  <si>
     <t>Unknown</t>
   </si>
   <si>
+    <t>single_table</t>
+  </si>
+  <si>
     <t>multi_table</t>
   </si>
   <si>
-    <t>single_table</t>
-  </si>
-  <si>
     <t>sdv</t>
   </si>
   <si>
@@ -157,21 +157,61 @@
     <t>World Bank</t>
   </si>
   <si>
+    <t>Statistical</t>
+  </si>
+  <si>
+    <t>Deep Learning</t>
+  </si>
+  <si>
     <t>Hierarchical Modeling</t>
   </si>
   <si>
     <t>Hierarchical Sampling</t>
   </si>
   <si>
-    <t>Statistical</t>
-  </si>
-  <si>
-    <t>Deep Learning</t>
-  </si>
-  <si>
     <t>No description available.</t>
   </si>
   <si>
+    <t xml:space="preserve">The BootstrapSynthesizer is a synthesizer specifically designed to work when you only have a few rows of data. This synthesizer internally bootstraps your real data, and then uses the bootstrapped data to build a model.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The CTGAN Synthesizer uses GAN-based, deep learning methods to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightweight statistical synthesizer that applies simple, column-wise models without learning inter-column dependencies.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Copula GAN Synthesizer uses a mix classic, statistical methods and GAN-based deep learning methods to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Gaussian Copula Synthesizer uses classic, statistical methods to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformer-based deep learning synthesizer that treats tabular data as a sequence modeling problem, inspired by large language models.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The SegmentSynthesizer calculates different segments of real data, and computes a different model for each one. You can supply any single-table synthesizer for computing the per-segment model. Use this when your real data is highly segmented, containing different patterns for each.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The TVAE Synthesizer uses a variational autoencoder (VAE)-based, neural network techniques to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statistical baseline synthesizer that generates values uniformly at random within the observed bounds of each column.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The XGCSynthesizer stands for eXtraGaussianCopula. It uses classic, statistical methods to train a model and generate synthetic data similar to the GaussianCopulaSynthesizer. However, it contains some additional features for higher quality modeling.
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">The HMA Synthesizer uses hierarchical ML algorithm to learn from real data and generate synthetic data.  The algorithm uses classical statistics.
 </t>
   </si>
@@ -185,46 +225,6 @@
   </si>
   <si>
     <t xml:space="preserve">Multi-table baseline synthesizer that generates data uniformly at random for each table while preserving table schemas.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The BootstrapSynthesizer is a synthesizer specifically designed to work when you only have a few rows of data. This synthesizer internally bootstraps your real data, and then uses the bootstrapped data to build a model.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The CTGAN Synthesizer uses GAN-based, deep learning methods to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightweight statistical synthesizer that applies simple, column-wise models without learning inter-column dependencies.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Copula GAN Synthesizer uses a mix classic, statistical methods and GAN-based deep learning methods to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Gaussian Copula Synthesizer uses classic, statistical methods to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformer-based deep learning synthesizer that treats tabular data as a sequence modeling problem, inspired by large language models.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The SegmentSynthesizer calculates different segments of real data, and computes a different model for each one. You can supply any single-table synthesizer for computing the per-segment model. Use this when your real data is highly segmented, containing different patterns for each.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The TVAE Synthesizer uses a variational autoencoder (VAE)-based, neural network techniques to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Statistical baseline synthesizer that generates values uniformly at random within the observed bounds of each column.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The XGCSynthesizer stands for eXtraGaussianCopula. It uses classic, statistical methods to train a model and generate synthetic data similar to the GaussianCopulaSynthesizer. However, it contains some additional features for higher quality modeling.
 </t>
   </si>
 </sst>
@@ -728,10 +728,10 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
         <v>40</v>
@@ -749,24 +749,24 @@
         <v>52</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
         <v>40</v>
@@ -784,48 +784,48 @@
         <v>53</v>
       </c>
       <c r="H6">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
         <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
         <v>45</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G7" t="s">
         <v>54</v>
       </c>
       <c r="H7">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
         <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
         <v>45</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G8" t="s">
         <v>55</v>
@@ -860,7 +860,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
@@ -868,13 +868,13 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
         <v>42</v>
@@ -883,13 +883,13 @@
         <v>45</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G9" t="s">
         <v>56</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -909,22 +909,22 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G10" t="s">
         <v>57</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -938,28 +938,28 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E11" t="s">
         <v>45</v>
       </c>
       <c r="F11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G11" t="s">
         <v>58</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -973,13 +973,13 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
         <v>42</v>
@@ -988,13 +988,13 @@
         <v>45</v>
       </c>
       <c r="F12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G12" t="s">
         <v>59</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1003,33 +1003,33 @@
         <v>0</v>
       </c>
       <c r="K12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E13" t="s">
         <v>45</v>
       </c>
       <c r="F13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G13" t="s">
         <v>60</v>
       </c>
       <c r="H13">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1043,28 +1043,28 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F14" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G14" t="s">
         <v>61</v>
       </c>
       <c r="H14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1073,15 +1073,15 @@
         <v>0</v>
       </c>
       <c r="K14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
         <v>41</v>
@@ -1099,24 +1099,24 @@
         <v>62</v>
       </c>
       <c r="H15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
         <v>41</v>
@@ -1134,13 +1134,13 @@
         <v>63</v>
       </c>
       <c r="H16">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
@@ -1148,34 +1148,34 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
         <v>41</v>
       </c>
       <c r="D17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E17" t="s">
         <v>45</v>
       </c>
       <c r="F17" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G17" t="s">
         <v>64</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
@@ -1183,37 +1183,37 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
         <v>41</v>
       </c>
       <c r="D18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E18" t="s">
         <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G18" t="s">
         <v>65</v>
       </c>
       <c r="H18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/assets/Model_Details.xlsx
+++ b/assets/Model_Details.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="68">
   <si>
     <t>Synthesizer</t>
   </si>
@@ -49,99 +49,105 @@
     <t>On the Pareto Curve</t>
   </si>
   <si>
+    <t>HMASynthesizer</t>
+  </si>
+  <si>
+    <t>HSASynthesizer</t>
+  </si>
+  <si>
+    <t>IndependentSynthesizer</t>
+  </si>
+  <si>
+    <t>MultiTableUniformSynthesizer</t>
+  </si>
+  <si>
     <t>BootstrapSynthesizer</t>
   </si>
   <si>
+    <t>CTGANSynthesizer</t>
+  </si>
+  <si>
+    <t>ColumnSynthesizer</t>
+  </si>
+  <si>
+    <t>CopulaGANSynthesizer</t>
+  </si>
+  <si>
+    <t>GaussianCopulaSynthesizer</t>
+  </si>
+  <si>
+    <t>RealTabFormerSynthesizer</t>
+  </si>
+  <si>
     <t>SegmentSynthesizer</t>
   </si>
   <si>
+    <t>TVAESynthesizer</t>
+  </si>
+  <si>
+    <t>TabDDPMSynthesizer</t>
+  </si>
+  <si>
+    <t>UniformSynthesizer</t>
+  </si>
+  <si>
     <t>XGCSynthesizer</t>
   </si>
   <si>
-    <t>CTGANSynthesizer</t>
-  </si>
-  <si>
-    <t>ColumnSynthesizer</t>
-  </si>
-  <si>
-    <t>CopulaGANSynthesizer</t>
-  </si>
-  <si>
-    <t>GaussianCopulaSynthesizer</t>
-  </si>
-  <si>
-    <t>RealTabFormerSynthesizer</t>
-  </si>
-  <si>
-    <t>TVAESynthesizer</t>
-  </si>
-  <si>
-    <t>UniformSynthesizer</t>
-  </si>
-  <si>
-    <t>HMASynthesizer</t>
-  </si>
-  <si>
-    <t>HSASynthesizer</t>
-  </si>
-  <si>
-    <t>IndependentSynthesizer</t>
-  </si>
-  <si>
-    <t>MultiTableUniformSynthesizer</t>
+    <t>HMA</t>
+  </si>
+  <si>
+    <t>HSA</t>
+  </si>
+  <si>
+    <t>Independent</t>
+  </si>
+  <si>
+    <t>MultiTableUniform</t>
   </si>
   <si>
     <t>Bootstrap</t>
   </si>
   <si>
+    <t>CTGAN</t>
+  </si>
+  <si>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>CopulaGAN</t>
+  </si>
+  <si>
+    <t>GaussianCopula</t>
+  </si>
+  <si>
+    <t>RealTabFormer</t>
+  </si>
+  <si>
     <t>Segment</t>
   </si>
   <si>
+    <t>TVAE</t>
+  </si>
+  <si>
+    <t>TabDDPM</t>
+  </si>
+  <si>
+    <t>Uniform</t>
+  </si>
+  <si>
     <t>XGC</t>
   </si>
   <si>
-    <t>CTGAN</t>
-  </si>
-  <si>
-    <t>Column</t>
-  </si>
-  <si>
-    <t>CopulaGAN</t>
-  </si>
-  <si>
-    <t>GaussianCopula</t>
-  </si>
-  <si>
-    <t>RealTabFormer</t>
-  </si>
-  <si>
-    <t>TVAE</t>
-  </si>
-  <si>
-    <t>Uniform</t>
-  </si>
-  <si>
-    <t>HMA</t>
-  </si>
-  <si>
-    <t>HSA</t>
-  </si>
-  <si>
-    <t>Independent</t>
-  </si>
-  <si>
-    <t>MultiTableUniform</t>
+    <t>multi_table</t>
+  </si>
+  <si>
+    <t>single_table</t>
   </si>
   <si>
     <t>Unknown</t>
   </si>
   <si>
-    <t>single_table</t>
-  </si>
-  <si>
-    <t>multi_table</t>
-  </si>
-  <si>
     <t>sdv</t>
   </si>
   <si>
@@ -157,74 +163,74 @@
     <t>World Bank</t>
   </si>
   <si>
+    <t>Hierarchical Modeling</t>
+  </si>
+  <si>
+    <t>Hierarchical Sampling</t>
+  </si>
+  <si>
     <t>Statistical</t>
   </si>
   <si>
     <t>Deep Learning</t>
   </si>
   <si>
-    <t>Hierarchical Modeling</t>
-  </si>
-  <si>
-    <t>Hierarchical Sampling</t>
+    <t xml:space="preserve">The HMA Synthesizer uses hierarchical ML algorithm to learn from real data and generate synthetic data.  The algorithm uses classical statistics.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The HSA Synthesizer uses a segment-based algorithm to learn from your real data and generate synthetic data. This synthesizer offers fast performance for unlimited tables.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Independent Synthesizer learns each table's patterns independently. This synthesizer offers fast performance for unlimited tables.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-table baseline synthesizer that generates data uniformly at random for each table while preserving table schemas.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The BootstrapSynthesizer is a synthesizer specifically designed to work when you only have a few rows of data. This synthesizer internally bootstraps your real data, and then uses the bootstrapped data to build a model.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The CTGAN Synthesizer uses GAN-based, deep learning methods to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightweight statistical synthesizer that applies simple, column-wise models without learning inter-column dependencies.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Copula GAN Synthesizer uses a mix classic, statistical methods and GAN-based deep learning methods to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Gaussian Copula Synthesizer uses classic, statistical methods to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformer-based deep learning synthesizer that treats tabular data as a sequence modeling problem, inspired by large language models.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The SegmentSynthesizer calculates different segments of real data, and computes a different model for each one. You can supply any single-table synthesizer for computing the per-segment model. Use this when your real data is highly segmented, containing different patterns for each.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The TVAE Synthesizer uses a variational autoencoder (VAE)-based, neural network techniques to train a model and generate synthetic data.
+</t>
   </si>
   <si>
     <t>No description available.</t>
   </si>
   <si>
-    <t xml:space="preserve">The BootstrapSynthesizer is a synthesizer specifically designed to work when you only have a few rows of data. This synthesizer internally bootstraps your real data, and then uses the bootstrapped data to build a model.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The CTGAN Synthesizer uses GAN-based, deep learning methods to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightweight statistical synthesizer that applies simple, column-wise models without learning inter-column dependencies.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Copula GAN Synthesizer uses a mix classic, statistical methods and GAN-based deep learning methods to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Gaussian Copula Synthesizer uses classic, statistical methods to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformer-based deep learning synthesizer that treats tabular data as a sequence modeling problem, inspired by large language models.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The SegmentSynthesizer calculates different segments of real data, and computes a different model for each one. You can supply any single-table synthesizer for computing the per-segment model. Use this when your real data is highly segmented, containing different patterns for each.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The TVAE Synthesizer uses a variational autoencoder (VAE)-based, neural network techniques to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">Statistical baseline synthesizer that generates values uniformly at random within the observed bounds of each column.
 </t>
   </si>
   <si>
     <t xml:space="preserve">The XGCSynthesizer stands for eXtraGaussianCopula. It uses classic, statistical methods to train a model and generate synthetic data similar to the GaussianCopulaSynthesizer. However, it contains some additional features for higher quality modeling.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The HMA Synthesizer uses hierarchical ML algorithm to learn from real data and generate synthetic data.  The algorithm uses classical statistics.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The HSA Synthesizer uses a segment-based algorithm to learn from your real data and generate synthetic data. This synthesizer offers fast performance for unlimited tables.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Independent Synthesizer learns each table's patterns independently. This synthesizer offers fast performance for unlimited tables.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-table baseline synthesizer that generates data uniformly at random for each table while preserving table schemas.
 </t>
   </si>
 </sst>
@@ -583,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -626,34 +632,34 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -661,31 +667,31 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="G3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
@@ -696,31 +702,31 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="G4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
@@ -728,25 +734,25 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -755,36 +761,36 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -793,33 +799,33 @@
         <v>0</v>
       </c>
       <c r="K6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F7" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -828,33 +834,33 @@
         <v>0</v>
       </c>
       <c r="K7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -863,33 +869,33 @@
         <v>0</v>
       </c>
       <c r="K8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G9" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H9">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -898,33 +904,33 @@
         <v>0</v>
       </c>
       <c r="K9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
         <v>44</v>
       </c>
       <c r="E10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F10" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G10" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -933,68 +939,68 @@
         <v>0</v>
       </c>
       <c r="K10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F11" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F12" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G12" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1008,28 +1014,28 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F13" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G13" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1043,177 +1049,107 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F14" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G14" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G15" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H15">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E16" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G16" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H16">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" t="s">
-        <v>42</v>
-      </c>
-      <c r="E17" t="s">
-        <v>45</v>
-      </c>
-      <c r="F17" t="s">
-        <v>47</v>
-      </c>
-      <c r="G17" t="s">
-        <v>64</v>
-      </c>
-      <c r="H17">
-        <v>60</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>2</v>
-      </c>
-      <c r="K17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" t="s">
-        <v>43</v>
-      </c>
-      <c r="E18" t="s">
-        <v>45</v>
-      </c>
-      <c r="F18" t="s">
-        <v>47</v>
-      </c>
-      <c r="G18" t="s">
-        <v>65</v>
-      </c>
-      <c r="H18">
-        <v>1</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>6</v>
-      </c>
-      <c r="K18" t="b">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/assets/Model_Details.xlsx
+++ b/assets/Model_Details.xlsx
@@ -49,6 +49,39 @@
     <t>On the Pareto Curve</t>
   </si>
   <si>
+    <t>BootstrapSynthesizer</t>
+  </si>
+  <si>
+    <t>CTGANSynthesizer</t>
+  </si>
+  <si>
+    <t>ColumnSynthesizer</t>
+  </si>
+  <si>
+    <t>CopulaGANSynthesizer</t>
+  </si>
+  <si>
+    <t>GaussianCopulaSynthesizer</t>
+  </si>
+  <si>
+    <t>RealTabFormerSynthesizer</t>
+  </si>
+  <si>
+    <t>SegmentSynthesizer</t>
+  </si>
+  <si>
+    <t>TVAESynthesizer</t>
+  </si>
+  <si>
+    <t>UniformSynthesizer</t>
+  </si>
+  <si>
+    <t>XGCSynthesizer</t>
+  </si>
+  <si>
+    <t>ClavaDDPMSynthesizer</t>
+  </si>
+  <si>
     <t>HMASynthesizer</t>
   </si>
   <si>
@@ -61,37 +94,37 @@
     <t>MultiTableUniformSynthesizer</t>
   </si>
   <si>
-    <t>BootstrapSynthesizer</t>
-  </si>
-  <si>
-    <t>CTGANSynthesizer</t>
-  </si>
-  <si>
-    <t>ColumnSynthesizer</t>
-  </si>
-  <si>
-    <t>CopulaGANSynthesizer</t>
-  </si>
-  <si>
-    <t>GaussianCopulaSynthesizer</t>
-  </si>
-  <si>
-    <t>RealTabFormerSynthesizer</t>
-  </si>
-  <si>
-    <t>SegmentSynthesizer</t>
-  </si>
-  <si>
-    <t>TVAESynthesizer</t>
-  </si>
-  <si>
-    <t>TabDDPMSynthesizer</t>
-  </si>
-  <si>
-    <t>UniformSynthesizer</t>
-  </si>
-  <si>
-    <t>XGCSynthesizer</t>
+    <t>Bootstrap</t>
+  </si>
+  <si>
+    <t>CTGAN</t>
+  </si>
+  <si>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>CopulaGAN</t>
+  </si>
+  <si>
+    <t>GaussianCopula</t>
+  </si>
+  <si>
+    <t>RealTabFormer</t>
+  </si>
+  <si>
+    <t>Segment</t>
+  </si>
+  <si>
+    <t>TVAE</t>
+  </si>
+  <si>
+    <t>Uniform</t>
+  </si>
+  <si>
+    <t>XGC</t>
+  </si>
+  <si>
+    <t>ClavaDDPM</t>
   </si>
   <si>
     <t>HMA</t>
@@ -106,48 +139,15 @@
     <t>MultiTableUniform</t>
   </si>
   <si>
-    <t>Bootstrap</t>
-  </si>
-  <si>
-    <t>CTGAN</t>
-  </si>
-  <si>
-    <t>Column</t>
-  </si>
-  <si>
-    <t>CopulaGAN</t>
-  </si>
-  <si>
-    <t>GaussianCopula</t>
-  </si>
-  <si>
-    <t>RealTabFormer</t>
-  </si>
-  <si>
-    <t>Segment</t>
-  </si>
-  <si>
-    <t>TVAE</t>
-  </si>
-  <si>
-    <t>TabDDPM</t>
-  </si>
-  <si>
-    <t>Uniform</t>
-  </si>
-  <si>
-    <t>XGC</t>
+    <t>single_table</t>
+  </si>
+  <si>
+    <t>Unknown</t>
   </si>
   <si>
     <t>multi_table</t>
   </si>
   <si>
-    <t>single_table</t>
-  </si>
-  <si>
-    <t>Unknown</t>
-  </si>
-  <si>
     <t>sdv</t>
   </si>
   <si>
@@ -163,16 +163,59 @@
     <t>World Bank</t>
   </si>
   <si>
+    <t>Statistical</t>
+  </si>
+  <si>
+    <t>Deep Learning</t>
+  </si>
+  <si>
     <t>Hierarchical Modeling</t>
   </si>
   <si>
     <t>Hierarchical Sampling</t>
   </si>
   <si>
-    <t>Statistical</t>
-  </si>
-  <si>
-    <t>Deep Learning</t>
+    <t xml:space="preserve">The BootstrapSynthesizer is a synthesizer specifically designed to work when you only have a few rows of data. This synthesizer internally bootstraps your real data, and then uses the bootstrapped data to build a model.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The CTGAN Synthesizer uses GAN-based, deep learning methods to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightweight statistical synthesizer that applies simple, column-wise models without learning inter-column dependencies.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Copula GAN Synthesizer uses a mix classic, statistical methods and GAN-based deep learning methods to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Gaussian Copula Synthesizer uses classic, statistical methods to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformer-based deep learning synthesizer that treats tabular data as a sequence modeling problem, inspired by large language models.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The SegmentSynthesizer calculates different segments of real data, and computes a different model for each one. You can supply any single-table synthesizer for computing the per-segment model. Use this when your real data is highly segmented, containing different patterns for each.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The TVAE Synthesizer uses a variational autoencoder (VAE)-based, neural network techniques to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statistical baseline synthesizer that generates values uniformly at random within the observed bounds of each column.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The XGCSynthesizer stands for eXtraGaussianCopula. It uses classic, statistical methods to train a model and generate synthetic data similar to the GaussianCopulaSynthesizer. However, it contains some additional features for higher quality modeling.
+</t>
+  </si>
+  <si>
+    <t>No description available.</t>
   </si>
   <si>
     <t xml:space="preserve">The HMA Synthesizer uses hierarchical ML algorithm to learn from real data and generate synthetic data.  The algorithm uses classical statistics.
@@ -188,49 +231,6 @@
   </si>
   <si>
     <t xml:space="preserve">Multi-table baseline synthesizer that generates data uniformly at random for each table while preserving table schemas.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The BootstrapSynthesizer is a synthesizer specifically designed to work when you only have a few rows of data. This synthesizer internally bootstraps your real data, and then uses the bootstrapped data to build a model.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The CTGAN Synthesizer uses GAN-based, deep learning methods to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightweight statistical synthesizer that applies simple, column-wise models without learning inter-column dependencies.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Copula GAN Synthesizer uses a mix classic, statistical methods and GAN-based deep learning methods to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Gaussian Copula Synthesizer uses classic, statistical methods to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformer-based deep learning synthesizer that treats tabular data as a sequence modeling problem, inspired by large language models.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The SegmentSynthesizer calculates different segments of real data, and computes a different model for each one. You can supply any single-table synthesizer for computing the per-segment model. Use this when your real data is highly segmented, containing different patterns for each.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The TVAE Synthesizer uses a variational autoencoder (VAE)-based, neural network techniques to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t>No description available.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Statistical baseline synthesizer that generates values uniformly at random within the observed bounds of each column.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The XGCSynthesizer stands for eXtraGaussianCopula. It uses classic, statistical methods to train a model and generate synthetic data similar to the GaussianCopulaSynthesizer. However, it contains some additional features for higher quality modeling.
 </t>
   </si>
 </sst>
@@ -650,16 +650,16 @@
         <v>53</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -685,16 +685,16 @@
         <v>54</v>
       </c>
       <c r="H3">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -708,25 +708,25 @@
         <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
         <v>47</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G4" t="s">
         <v>55</v>
       </c>
       <c r="H4">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
@@ -743,13 +743,13 @@
         <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E5" t="s">
         <v>47</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G5" t="s">
         <v>56</v>
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
         <v>44</v>
@@ -784,13 +784,13 @@
         <v>47</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G6" t="s">
         <v>57</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -810,28 +810,28 @@
         <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G7" t="s">
         <v>58</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
@@ -845,22 +845,22 @@
         <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
         <v>47</v>
       </c>
       <c r="F8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G8" t="s">
         <v>59</v>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -880,7 +880,7 @@
         <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
         <v>44</v>
@@ -889,13 +889,13 @@
         <v>47</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G9" t="s">
         <v>60</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -915,22 +915,22 @@
         <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s">
         <v>47</v>
       </c>
       <c r="F10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G10" t="s">
         <v>61</v>
       </c>
       <c r="H10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -950,31 +950,31 @@
         <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F11" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G11" t="s">
         <v>62</v>
       </c>
       <c r="H11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -991,25 +991,25 @@
         <v>44</v>
       </c>
       <c r="E12" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="G12" t="s">
         <v>63</v>
       </c>
       <c r="H12">
+        <v>10</v>
+      </c>
+      <c r="I12">
         <v>6</v>
       </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
       <c r="J12">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="K12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1020,7 +1020,7 @@
         <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
         <v>44</v>
@@ -1029,22 +1029,22 @@
         <v>47</v>
       </c>
       <c r="F13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G13" t="s">
         <v>64</v>
       </c>
       <c r="H13">
+        <v>6</v>
+      </c>
+      <c r="I13">
         <v>5</v>
       </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
       <c r="J13">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="K13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1061,25 +1061,25 @@
         <v>44</v>
       </c>
       <c r="E14" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F14" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="G14" t="s">
         <v>65</v>
       </c>
       <c r="H14">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
         <v>2</v>
       </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
       <c r="K14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1090,28 +1090,28 @@
         <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E15" t="s">
         <v>47</v>
       </c>
       <c r="F15" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G15" t="s">
         <v>66</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
@@ -1125,28 +1125,28 @@
         <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E16" t="s">
         <v>47</v>
       </c>
       <c r="F16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G16" t="s">
         <v>67</v>
       </c>
       <c r="H16">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
